--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_31-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_31-07-2025.xlsx
@@ -591,27 +591,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -712,27 +712,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -833,27 +833,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -926,7 +926,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>£16.70</t>
+          <t>£16.60</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -954,27 +954,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -1075,27 +1075,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -1196,27 +1196,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -1317,27 +1317,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -1438,27 +1438,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -1559,27 +1559,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>£28.99</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1680,27 +1680,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -1801,27 +1801,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -1922,27 +1922,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -2043,27 +2043,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -2164,27 +2164,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -2285,27 +2285,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>£653.19</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-xr4165-165mm/</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2503,27 +2503,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -2624,27 +2624,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -2745,27 +2745,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -2866,27 +2866,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -2987,27 +2987,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -3108,27 +3108,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -3229,27 +3229,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -3350,27 +3350,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
@@ -3471,33 +3471,33 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.183); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c43e415+77285]
-	GetHandleVerifier [0x0x7ff61c43e470+77376]
-	(No symbol) [0x0x7ff61c209a6a]
-	(No symbol) [0x0x7ff61c260406]
-	(No symbol) [0x0x7ff61c2606bc]
-	(No symbol) [0x0x7ff61c2b3ac7]
-	(No symbol) [0x0x7ff61c28864f]
-	(No symbol) [0x0x7ff61c2b087f]
-	(No symbol) [0x0x7ff61c2883e3]
-	(No symbol) [0x0x7ff61c251521]
-	(No symbol) [0x0x7ff61c2522b3]
-	GetHandleVerifier [0x0x7ff61c721efd+3107021]
-	GetHandleVerifier [0x0x7ff61c71c29d+3083373]
-	GetHandleVerifier [0x0x7ff61c73bedd+3213485]
-	GetHandleVerifier [0x0x7ff61c45884e+184862]
-	GetHandleVerifier [0x0x7ff61c46055f+216879]
-	GetHandleVerifier [0x0x7ff61c447084+113236]
-	GetHandleVerifier [0x0x7ff61c447239+113673]
-	GetHandleVerifier [0x0x7ff61c42e298+11368]
-	BaseThreadInitThunk [0x0x7ffc07fce8d7+23]
-	RtlUserThreadStart [0x0x7ffc093fc34c+44]
+	GetHandleVerifier [0x0x7ff7088be415+77285]
+	GetHandleVerifier [0x0x7ff7088be470+77376]
+	(No symbol) [0x0x7ff708689a6a]
+	(No symbol) [0x0x7ff7086e0406]
+	(No symbol) [0x0x7ff7086e06bc]
+	(No symbol) [0x0x7ff708733ac7]
+	(No symbol) [0x0x7ff70870864f]
+	(No symbol) [0x0x7ff70873087f]
+	(No symbol) [0x0x7ff7087083e3]
+	(No symbol) [0x0x7ff7086d1521]
+	(No symbol) [0x0x7ff7086d22b3]
+	GetHandleVerifier [0x0x7ff708ba1efd+3107021]
+	GetHandleVerifier [0x0x7ff708b9c29d+3083373]
+	GetHandleVerifier [0x0x7ff708bbbedd+3213485]
+	GetHandleVerifier [0x0x7ff7088d884e+184862]
+	GetHandleVerifier [0x0x7ff7088e055f+216879]
+	GetHandleVerifier [0x0x7ff7088c7084+113236]
+	GetHandleVerifier [0x0x7ff7088c7239+113673]
+	GetHandleVerifier [0x0x7ff7088ae298+11368]
+	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
+	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>£40.53</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-cw4100-100mm/</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>£1057.71</t>
+          <t>Error: 504 Server Error: Gateway Time-out for url: https://www.insulation-online.com/product/celotex-thermaclass-cavity-wall-21-90mm/</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>£1126.15</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-thermaclass-cavity-wall-21-115mm/</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
